--- a/Outputs/Recycling_Plot_Data/ACCII/02_National_Stacked_2050_data_ACCII.xlsx
+++ b/Outputs/Recycling_Plot_Data/ACCII/02_National_Stacked_2050_data_ACCII.xlsx
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.7496032910202518</v>
+        <v>0.7488521272651167</v>
       </c>
     </row>
     <row r="5">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.413464627302696</v>
+        <v>0.4130529059331819</v>
       </c>
     </row>
     <row r="6">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>1.403681196479397</v>
+        <v>1.402274593211788</v>
       </c>
     </row>
     <row r="7">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.774239560720494</v>
+        <v>0.7734685855240151</v>
       </c>
     </row>
     <row r="8">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.08671258408835963</v>
+        <v>0.08662569099295631</v>
       </c>
     </row>
     <row r="15">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.04782874714137119</v>
+        <v>0.04778112005074519</v>
       </c>
     </row>
     <row r="16">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.6659696282424172</v>
+        <v>0.6659083560325868</v>
       </c>
     </row>
     <row r="19">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.3939349635357499</v>
+        <v>0.3938971315660474</v>
       </c>
     </row>
     <row r="20">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="D22">
-        <v>11.81286824521793</v>
+        <v>11.79944174288671</v>
       </c>
     </row>
     <row r="23">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="D23">
-        <v>6.536850974819679</v>
+        <v>6.529491756686741</v>
       </c>
     </row>
     <row r="24">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="D24">
-        <v>12.53681662223244</v>
+        <v>12.52425370746911</v>
       </c>
     </row>
     <row r="25">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="D25">
-        <v>6.915031289708594</v>
+        <v>6.908145413711402</v>
       </c>
     </row>
     <row r="26">
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="D26">
-        <v>7.038781999765233</v>
+        <v>7.031728564992661</v>
       </c>
     </row>
     <row r="27">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="D27">
-        <v>3.882436764967768</v>
+        <v>3.87857069740994</v>
       </c>
     </row>
     <row r="28">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="D28">
-        <v>6.350599542722977</v>
+        <v>6.339941640358806</v>
       </c>
     </row>
     <row r="29">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="D29">
-        <v>3.813774874015224</v>
+        <v>3.806961237850846</v>
       </c>
     </row>
     <row r="30">
